--- a/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
@@ -8,10 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座 销控表" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -114,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -179,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -195,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1958,7 +1819,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2509,23 +2370,27 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>39048000</v>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>30917</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3801,23 +3666,27 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="n">
-        <v>37850000</v>
-      </c>
-      <c r="I70" s="5" t="n">
-        <v>29968</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11750,7 +11619,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -30264,6504 +30133,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Blue Coast - 1A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>116 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>103 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,634万
-$26,187/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,687万
-$27,906/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$4,624万
-$36,615/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$4,358万
-$34,400/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,621万
-$26,056/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,661万
-$27,630/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$4,408万
-$34,900/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$4,434万
-$35,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,608万
-$25,928/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,634万
-$27,355/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$4,231万
-$33,500/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$4,080万
-$32,200/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,595万
-$25,798/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,716万
-$28,200/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$4,181万
-$33,100/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$4,029万
-$31,800/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,561万
-$25,456/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,582万
-$26,817/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$4,130万
-$32,700/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3,978万
-$31,400/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,536万
-$25,205/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,662万
-$27,645/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$4,092万
-$32,400/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3,940万
-$31,100/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,523万
-$25,080/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,596万
-$26,952/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,821万
-$30,250/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3,978万
-$31,400/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,510万
-$24,953/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,583万
-$26,818/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,769万
-$29,842/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,488万
-$24,727/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,570万
-$26,685/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,905万
-$30,917/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3,953万
-$31,200/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,475万
-$24,602/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,557万
-$26,552/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,886万
-$30,764/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3,928万
-$31,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,463万
-$24,480/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,444万
-$25,375/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,866万
-$30,610/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3,902万
-$30,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,450万
-$24,359/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,532万
-$26,288/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,847万
-$30,458/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3,890万
-$30,700/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,342万
-$23,278/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,508万
-$26,049/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,828万
-$30,308/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,422万
-$24,077/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,496万
-$25,920/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,663万
-$29,006/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3,961万
-$31,259/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,410万
-$23,956/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,386万
-$24,772/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 1264呎 (4+房)
-$3,804万
-$30,093/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$4,164万
-$32,865/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,303万
-$22,895/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,471万
-$25,663/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,785万
-$29,968/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3,750万
-$29,600/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,292万
-$22,781/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,459万
-$25,536/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,766万
-$29,819/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3,725万
-$29,400/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,358万
-$23,441/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,447万
-$25,408/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,747万
-$29,671/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3,712万
-$29,300/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,347万
-$23,326/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,338万
-$24,282/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,720万
-$29,450/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 1238呎 (4+房)
-$3,677万
-$29,700/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,335万
-$23,209/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,462万
-$25,564/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,827万
-$30,300/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3,776万
-$29,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,323万
-$23,093/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,437万
-$25,309/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,890万
-$30,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,312万
-$22,979/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,425万
-$25,183/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,814万
-$30,200/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-$3,636万
-$28,700/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,209万
-$21,960/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,413万
-$25,058/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,802万
-$30,100/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,279万
-$22,655/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,401万
-$24,933/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,776万
-$29,900/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,268万
-$22,542/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,389万
-$24,809/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,776万
-$29,900/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,245万
-$22,319/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,377万
-$24,685/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,223万
-$22,096/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,260万
-$23,474/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>A | 1263呎 (4+房)
-$3,776万
-$29,900/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 1267呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,179万
-$21,664/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>D | 963呎 (3房)
-$2,314万
-$24,030/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>A | 1226呎 (4+房)
-$3,984万
-$32,500/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>B | 1229呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>C | 1006呎 (3房)
-$2,137万
-$21,240/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>D | 938呎 (3房)
-$2,466万
-$26,287/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Blue Coast - 1B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>116 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>116 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,574万
-$26,866/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,579万
-$26,923/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,490万
-$25,618/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,758万
-$28,380/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,542万
-$26,538/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,566万
-$26,789/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,461万
-$25,316/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,634万
-$27,101/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,515万
-$26,248/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,554万
-$26,657/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,433万
-$25,027/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,716万
-$27,937/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,482万
-$25,911/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,440万
-$25,475/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,408万
-$24,779/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,677万
-$27,545/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,449万
-$25,567/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,426万
-$25,325/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,397万
-$24,656/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,514万
-$25,865/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,321万
-$24,230/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,404万
-$25,097/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,373万
-$24,413/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,570万
-$26,439/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,401万
-$25,064/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,489万
-$25,977/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,361万
-$24,290/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,410万
-$24,794/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,283万
-$23,835/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,476万
-$25,848/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,349万
-$24,169/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,497万
-$25,687/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,354万
-$24,569/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,464万
-$25,718/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,338万
-$24,049/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,386万
-$24,548/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,342万
-$24,448/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,452万
-$25,591/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,326万
-$23,930/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,472万
-$25,431/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,330万
-$24,326/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,340万
-$24,423/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,314万
-$23,810/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,460万
-$25,306/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,319万
-$24,205/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,424万
-$25,301/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,303万
-$23,692/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,441万
-$25,117/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,307万
-$24,085/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,316万
-$24,178/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,201万
-$22,642/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,429万
-$24,993/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,296万
-$23,966/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,400万
-$25,049/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,280万
-$23,456/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,417万
-$24,869/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,284万
-$23,846/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,293万
-$23,939/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,269万
-$23,340/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,405万
-$24,746/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,273万
-$23,727/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,376万
-$24,802/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,168万
-$22,306/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,393万
-$24,622/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,262万
-$23,609/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,271万
-$23,701/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,246万
-$23,108/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,379万
-$24,475/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,250万
-$23,492/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,352万
-$24,555/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,235万
-$22,993/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,274万
-$23,392/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,239万
-$23,375/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,341万
-$24,433/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,224万
-$22,878/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,262万
-$23,276/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,228万
-$23,259/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,234万
-$23,317/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,213万
-$22,764/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,344万
-$24,112/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,206万
-$23,027/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,314万
-$24,156/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,576万
-$26,502/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,240万
-$23,047/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,108万
-$22,007/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,303万
-$24,037/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,191万
-$22,538/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,727万
-$28,055/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,184万
-$22,801/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,291万
-$23,916/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,180万
-$22,426/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,309万
-$23,757/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,087万
-$21,788/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,280万
-$23,797/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,172万
-$22,347/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,298万
-$23,638/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,162万
-$22,573/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,265万
-$23,645/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,164万
-$22,259/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,286万
-$23,521/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,152万
-$22,461/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,243万
-$23,410/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,057万
-$21,166/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,275万
-$23,404/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,130万
-$22,239/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,133万
-$22,262/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,037万
-$20,956/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,252万
-$23,172/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,109万
-$22,019/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,175万
-$22,704/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,095万
-$21,550/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,142万
-$22,036/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>A | 958呎 (3房)
-$2,237万
-$23,347/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>B | 958呎 (3房)
-$2,367万
-$24,705/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>C | 972呎 (3房)
-$2,157万
-$22,192/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>D | 972呎 (3房)
-$2,186万
-$22,493/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Blue Coast - 2A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>180 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>180 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$2,027万
-$26,226/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$2,212万
-$28,620/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,881万
-$25,183/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$2,008万
-$27,578/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,951万
-$26,472/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$2,100万
-$28,082/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$2,012万
-$26,035/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$2,068万
-$26,758/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,865万
-$24,971/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,988万
-$27,309/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,849万
-$25,087/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$2,080万
-$27,803/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,987万
-$25,709/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$2,130万
-$27,558/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,849万
-$24,750/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,978万
-$27,173/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,898万
-$25,760/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,969万
-$26,329/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$2,058万
-$26,618/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$2,120万
-$27,420/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,830万
-$24,503/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,968万
-$27,037/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,870万
-$25,377/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$2,027万
-$27,095/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$2,034万
-$26,309/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$2,038万
-$26,361/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,745万
-$23,359/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,958万
-$26,902/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,847万
-$25,064/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$2,002万
-$26,759/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$2,026万
-$26,208/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$2,025万
-$26,191/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,736万
-$23,244/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,949万
-$26,769/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,756万
-$23,833/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,973万
-$26,382/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$2,023万
-$26,173/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,925万
-$24,907/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,790万
-$23,959/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$2,075万
-$28,500/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,811万
-$24,569/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,954万
-$26,122/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,934万
-$25,014/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,995万
-$25,803/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,781万
-$23,839/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,969万
-$27,051/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,802万
-$24,445/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,928万
-$25,771/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$2,003万
-$25,913/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$2,085万
-$26,974/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,772万
-$23,722/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,906万
-$26,179/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,793万
-$24,324/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,834万
-$24,524/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,914万
-$24,765/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$2,075万
-$26,838/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,763万
-$23,605/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,896万
-$26,045/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,713万
-$23,247/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,810万
-$24,191/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,983万
-$25,656/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,887万
-$24,414/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,754万
-$23,486/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,879万
-$25,816/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,705万
-$23,130/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,784万
-$23,854/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,973万
-$25,529/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$2,009万
-$25,990/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,746万
-$23,371/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,870万
-$25,687/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,766万
-$23,965/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,849万
-$24,715/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,964万
-$25,401/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,864万
-$24,114/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,972万
-$26,394/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,861万
-$25,559/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,757万
-$23,844/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,839万
-$24,591/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,954万
-$25,276/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,855万
-$23,994/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,728万
-$23,138/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,735万
-$23,831/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,749万
-$23,726/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,830万
-$24,468/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,867万
-$24,157/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,921万
-$24,856/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,720万
-$23,021/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,842万
-$25,305/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,740万
-$23,607/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,821万
-$24,348/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,934万
-$25,025/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,834万
-$23,721/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,711万
-$22,908/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,833万
-$25,181/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,731万
-$23,490/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,812万
-$24,223/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,925万
-$24,900/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,900万
-$24,574/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,636万
-$21,894/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,709万
-$23,478/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,723万
-$23,373/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,803万
-$24,104/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,907万
-$24,670/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,815万
-$23,484/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,694万
-$22,681/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,701万
-$23,361/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,714万
-$23,258/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,794万
-$23,984/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,826万
-$23,617/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,881万
-$24,331/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,686万
-$22,569/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,762万
-$24,202/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,638万
-$22,225/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,785万
-$23,865/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,808万
-$23,383/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,871万
-$24,208/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,678万
-$22,456/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,753万
-$24,081/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,689万
-$22,912/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,767万
-$23,628/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,798万
-$23,266/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,858万
-$24,032/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,920万
-$25,696/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,708万
-$23,466/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,680万
-$22,799/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,759万
-$23,512/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,786万
-$23,111/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,848万
-$23,911/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,661万
-$22,233/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,700万
-$23,348/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,606万
-$21,787/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,750万
-$23,396/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,778万
-$22,995/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,766万
-$22,853/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,653万
-$22,123/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,691万
-$23,231/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,664万
-$22,573/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,959万
-$26,187/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,761万
-$22,781/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,830万
-$23,675/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,581万
-$21,162/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,616万
-$22,203/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,657万
-$22,482/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,949万
-$26,059/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,832万
-$23,705/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,749万
-$22,625/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,638万
-$21,934/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,674万
-$23,000/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,650万
-$22,383/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,724万
-$23,047/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,751万
-$22,656/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,812万
-$23,440/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,630万
-$21,826/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,666万
-$22,887/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,641万
-$22,270/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,716万
-$22,934/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,814万
-$23,470/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,794万
-$23,207/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,620万
-$21,685/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,650万
-$22,661/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,633万
-$22,160/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,707万
-$22,818/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,796万
-$23,238/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,714万
-$22,179/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,608万
-$21,525/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,576万
-$21,655/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,623万
-$22,016/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,690万
-$22,592/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,778万
-$23,008/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,763万
-$22,806/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,600万
-$21,418/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,625万
-$22,324/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,611万
-$21,853/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,673万
-$22,369/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>A | 773呎 (3房)
-$1,943万
-$25,140/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>B | 773呎 (3房)
-$1,728万
-$22,360/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>C | 747呎 (3房)
-$1,706万
-$22,834/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>D | 728呎 (3房)
-$1,536万
-$21,099/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,669万
-$22,649/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>F | 748呎 (3房)
-$1,777万
-$23,761/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Blue Coast - 2B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>230 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>230 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$2,011万
-$26,816/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,376万
-$25,578/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,430万
-$26,584/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$1,148万
-$25,387/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$1,982万
-$25,019/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,121万
-$24,692/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$2,028万
-$26,005/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$2,051万
-$27,491/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,991万
-$26,552/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,369万
-$25,448/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,367万
-$25,407/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$1,142万
-$25,261/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$2,011万
-$25,394/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,161万
-$25,577/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$2,017万
-$25,862/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,912万
-$25,629/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$2,070万
-$27,604/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,418万
-$26,364/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,360万
-$25,281/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$1,183万
-$26,170/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$2,001万
-$25,266/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,156万
-$25,452/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$2,002万
-$25,673/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,968万
-$26,374/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$2,032万
-$27,100/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,398万
-$25,981/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,395万
-$25,935/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$1,167万
-$25,827/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$1,991万
-$25,140/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,150万
-$25,324/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$1,986万
-$25,463/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,943万
-$26,046/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,933万
-$25,771/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,387万
-$25,784/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,330万
-$24,725/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$1,111万
-$24,582/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$1,981万
-$25,015/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,140万
-$25,104/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$1,975万
-$25,322/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,843万
-$24,705/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,911万
-$25,479/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,375万
-$25,554/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,318万
-$24,504/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$1,142万
-$25,259/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$1,971万
-$24,891/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,134万
-$24,978/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$1,964万
-$25,179/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,897万
-$25,424/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,970万
-$26,263/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,356万
-$25,197/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,353万
-$25,154/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$1,081万
-$23,920/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$2,238万
-$28,263/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,128万
-$24,852/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$1,944万
-$24,928/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,878万
-$25,173/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,960万
-$26,135/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,285万
-$23,883/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,336万
-$24,823/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$1,116万
-$24,679/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$1,896万
-$23,937/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,123万
-$24,731/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$1,926万
-$24,697/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,787万
-$23,953/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,873万
-$24,975/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,326万
-$24,638/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,323万
-$24,597/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$1,066万
-$23,586/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$1,870万
-$23,612/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,073万
-$23,634/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$1,909万
-$24,469/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,770万
-$23,731/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,864万
-$24,852/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,277万
-$23,729/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,306万
-$24,270/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$1,069万
-$23,648/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$1,772万
-$22,369/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,112万
-$24,485/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$1,890万
-$24,233/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,746万
-$23,408/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,931万
-$25,747/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,269万
-$23,589/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,297万
-$24,110/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$1,020万
-$22,577/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$1,827万
-$23,072/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,062万
-$23,401/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$1,881万
-$24,113/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,793万
-$24,036/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,841万
-$24,545/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,258万
-$23,379/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,282万
-$23,827/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$1,012万
-$22,378/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$1,810万
-$22,855/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,098万
-$24,189/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$1,797万
-$23,044/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,776万
-$23,810/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,832万
-$24,424/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,244万
-$23,126/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,319万
-$24,509/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$1,042万
-$23,046/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$1,801万
-$22,742/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,030万
-$22,676/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$1,788万
-$22,929/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,698万
-$22,755/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,898万
-$25,301/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,233万
-$22,922/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,260万
-$23,422/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$1,033万
-$22,845/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$1,721万
-$21,734/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,058万
-$23,304/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$1,853万
-$23,754/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,759万
-$23,575/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,888万
-$25,177/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,218万
-$22,638/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,306万
-$24,268/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$980万
-$21,670/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$1,783万
-$22,516/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,212万
-$26,690/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$1,844万
-$23,636/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,750万
-$23,457/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,876万
-$25,016/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,155万
-$21,476/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,299万
-$24,145/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$1,007万
-$22,283/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$1,774万
-$22,403/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,041万
-$22,923/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$2,064万
-$26,459/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,741万
-$23,339/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,867万
-$24,891/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,194万
-$22,193/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,290万
-$23,968/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$1,000万
-$22,119/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$1,766万
-$22,292/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,034万
-$22,771/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$2,112万
-$27,072/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,664万
-$22,306/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,858万
-$24,768/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,141万
-$21,208/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,232万
-$22,905/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$995万
-$22,007/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$1,757万
-$22,181/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$1,016万
-$22,381/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$1,816万
-$23,286/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,724万
-$23,107/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,775万
-$23,668/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,135万
-$21,102/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,277万
-$23,730/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$990万
-$21,898/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$1,748万
-$22,071/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$998万
-$21,991/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$1,807万
-$23,171/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,715万
-$22,992/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,830万
-$24,399/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,176万
-$21,864/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,218万
-$22,647/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$946万
-$20,929/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 792呎 (3房)
-$1,739万
-$21,961/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 454呎 (2房)
-$993万
-$21,879/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>G | 780呎 (3房)
-$1,789万
-$22,941/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,698万
-$22,764/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,816万
-$24,220/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,170万
-$21,753/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,572万
-$29,224/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$980万
-$21,681/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 813呎 (3房)
-$1,664万
-$20,462/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G26" s="19" t="inlineStr"/>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>G | 796呎 (3房)
-$1,772万
-$22,256/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,690万
-$22,650/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,808万
-$24,100/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,118万
-$20,788/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,256万
-$23,342/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$975万
-$21,575/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 813呎 (3房)
-$1,655万
-$20,360/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G27" s="19" t="inlineStr"/>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>G | 796呎 (3房)
-$1,693万
-$21,270/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,681万
-$22,539/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,798万
-$23,980/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,159万
-$21,537/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,197万
-$22,255/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$970万
-$21,465/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 813呎 (3房)
-$1,715万
-$21,093/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G28" s="19" t="inlineStr"/>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>G | 796呎 (3房)
-$1,685万
-$21,163/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,673万
-$22,425/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,790万
-$23,861/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,153万
-$21,431/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,240万
-$23,058/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$965万
-$21,358/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>E | 813呎 (3房)
-$1,706万
-$20,989/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G29" s="19" t="inlineStr"/>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>G | 796呎 (3房)
-$1,676万
-$21,060/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,599万
-$21,432/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,781万
-$23,741/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,102万
-$20,481/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,234万
-$22,944/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$923万
-$20,412/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>E | 813呎 (3房)
-$1,698万
-$20,884/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G30" s="19" t="inlineStr"/>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>G | 796呎 (3房)
-$1,668万
-$20,954/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,591万
-$21,326/呎
-(24年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,772万
-$23,624/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,143万
-$21,238/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,228万
-$22,829/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$957万
-$21,170/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>E | 813呎 (3房)
-$1,785万
-$21,956/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="G31" s="19" t="inlineStr"/>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>G | 796呎 (3房)
-$1,660万
-$20,849/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,813万
-$24,303/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,763万
-$23,505/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,132万
-$21,039/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,528万
-$28,400/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$948万
-$20,969/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>E | 813呎 (3房)
-$1,673万
-$20,574/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G32" s="19" t="inlineStr"/>
-      <c r="H32" s="17" t="inlineStr">
-        <is>
-          <t>G | 796呎 (3房)
-$1,651万
-$20,746/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,640万
-$21,983/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,676万
-$22,353/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,082万
-$20,108/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,207万
-$22,437/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$943万
-$20,865/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>E | 813呎 (3房)
-$1,663万
-$20,454/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G33" s="19" t="inlineStr"/>
-      <c r="H33" s="17" t="inlineStr">
-        <is>
-          <t>G | 796呎 (3房)
-$1,635万
-$20,540/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,624万
-$21,764/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,656万
-$22,079/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,113万
-$20,695/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,195万
-$22,214/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$932万
-$20,626/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>E | 813呎 (3房)
-$1,642万
-$20,202/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G34" s="19" t="inlineStr"/>
-      <c r="H34" s="17" t="inlineStr">
-        <is>
-          <t>G | 796呎 (3房)
-$1,619万
-$20,338/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,608万
-$21,550/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>A | 750呎 (3房)
-$1,690万
-$22,539/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>B | 538呎 (2房)
-$1,092万
-$20,290/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>C | 538呎 (2房)
-$1,125万
-$20,918/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>D | 452呎 (2房)
-$914万
-$20,223/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>E | 813呎 (3房)
-$1,544万
-$18,998/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G35" s="19" t="inlineStr"/>
-      <c r="H35" s="17" t="inlineStr">
-        <is>
-          <t>G | 796呎 (3房)
-$1,652万
-$20,760/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>H | 746呎 (3房)
-$1,576万
-$21,126/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
@@ -8,6 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +45,102 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +151,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +232,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +665,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -30133,4 +30324,6504 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2634万
+$26,187/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2687万
+$27,906/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$4624万
+$36,615/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$4358万
+$34,400/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2621万
+$26,056/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2661万
+$27,630/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$4408万
+$34,900/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$4434万
+$35,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2608万
+$25,928/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2634万
+$27,355/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$4231万
+$33,500/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$4080万
+$32,200/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2595万
+$25,798/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2716万
+$28,200/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$4181万
+$33,100/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$4029万
+$31,800/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2561万
+$25,456/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2582万
+$26,817/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$4130万
+$32,700/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3978万
+$31,400/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2536万
+$25,205/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2662万
+$27,645/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$4092万
+$32,400/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3940万
+$31,100/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2523万
+$25,080/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2596万
+$26,952/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3821万
+$30,250/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3978万
+$31,400/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2510万
+$24,953/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2583万
+$26,818/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3769万
+$29,842/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2488万
+$24,727/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2570万
+$26,685/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+招标单位
+-
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3953万
+$31,200/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2475万
+$24,602/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2557万
+$26,552/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3886万
+$30,764/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3928万
+$31,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2463万
+$24,480/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2444万
+$25,375/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3866万
+$30,610/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3902万
+$30,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2450万
+$24,359/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2532万
+$26,288/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3847万
+$30,458/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3890万
+$30,700/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2342万
+$23,278/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2508万
+$26,049/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3828万
+$30,308/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2422万
+$24,077/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2496万
+$25,920/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3663万
+$29,006/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3961万
+$31,259/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2410万
+$23,956/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2386万
+$24,772/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 1264呎 (4+房)
+$3804万
+$30,093/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$4164万
+$32,865/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2303万
+$22,895/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2471万
+$25,663/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+招标单位
+-
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3750万
+$29,600/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2292万
+$22,781/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2459万
+$25,536/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3766万
+$29,819/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3725万
+$29,400/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2358万
+$23,441/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2447万
+$25,408/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3747万
+$29,671/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3712万
+$29,300/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2347万
+$23,326/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2338万
+$24,282/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3720万
+$29,450/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 1238呎 (4+房)
+$3677万
+$29,700/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2335万
+$23,209/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2462万
+$25,564/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3827万
+$30,300/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3776万
+$29,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2323万
+$23,093/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2437万
+$25,309/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3890万
+$30,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2312万
+$22,979/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2425万
+$25,183/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3814万
+$30,200/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+$3636万
+$28,700/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2209万
+$21,960/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2413万
+$25,058/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3802万
+$30,100/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2279万
+$22,655/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2401万
+$24,933/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3776万
+$29,900/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2268万
+$22,542/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2389万
+$24,809/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3776万
+$29,900/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2245万
+$22,319/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2377万
+$24,685/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2223万
+$22,096/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2260万
+$23,474/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>A | 1263呎 (4+房)
+$3776万
+$29,900/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 1267呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2179万
+$21,664/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>D | 963呎 (3房)
+$2314万
+$24,030/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>A | 1226呎 (4+房)
+$3984万
+$32,500/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 1229呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>C | 1006呎 (3房)
+$2137万
+$21,240/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>D | 938呎 (3房)
+$2466万
+$26,287/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2574万
+$26,866/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2579万
+$26,923/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2490万
+$25,618/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2758万
+$28,380/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2542万
+$26,538/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2566万
+$26,789/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2461万
+$25,316/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2634万
+$27,101/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2515万
+$26,248/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2554万
+$26,657/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2433万
+$25,027/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2716万
+$27,937/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2482万
+$25,911/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2440万
+$25,475/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2408万
+$24,779/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2677万
+$27,545/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2449万
+$25,567/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2426万
+$25,325/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2397万
+$24,656/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2514万
+$25,865/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2321万
+$24,230/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2404万
+$25,097/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2373万
+$24,413/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2570万
+$26,439/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2401万
+$25,064/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2489万
+$25,977/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2361万
+$24,290/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2410万
+$24,794/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2283万
+$23,835/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2476万
+$25,848/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2349万
+$24,169/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2497万
+$25,687/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2354万
+$24,569/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2464万
+$25,718/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2338万
+$24,049/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2386万
+$24,548/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2342万
+$24,448/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2452万
+$25,591/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2326万
+$23,930/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2472万
+$25,431/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2330万
+$24,326/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2340万
+$24,423/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2314万
+$23,810/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2460万
+$25,306/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2319万
+$24,205/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2424万
+$25,301/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2303万
+$23,692/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2441万
+$25,117/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2307万
+$24,085/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2316万
+$24,178/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2201万
+$22,642/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2429万
+$24,993/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2296万
+$23,966/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2400万
+$25,049/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2280万
+$23,456/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2417万
+$24,869/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2284万
+$23,846/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2293万
+$23,939/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2269万
+$23,340/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2405万
+$24,746/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2273万
+$23,727/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2376万
+$24,802/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2168万
+$22,306/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2393万
+$24,622/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2262万
+$23,609/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2271万
+$23,701/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2246万
+$23,108/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2379万
+$24,475/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2250万
+$23,492/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2352万
+$24,555/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2235万
+$22,993/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2274万
+$23,392/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2239万
+$23,375/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2341万
+$24,433/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2224万
+$22,878/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2262万
+$23,276/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2228万
+$23,259/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2234万
+$23,317/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2213万
+$22,764/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2344万
+$24,112/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2206万
+$23,027/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2314万
+$24,156/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2576万
+$26,502/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2240万
+$23,047/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2108万
+$22,007/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2303万
+$24,037/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2191万
+$22,538/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2727万
+$28,055/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2184万
+$22,801/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2291万
+$23,916/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2180万
+$22,426/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2309万
+$23,757/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2087万
+$21,788/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2280万
+$23,797/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2172万
+$22,347/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2298万
+$23,638/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2162万
+$22,573/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2265万
+$23,645/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2164万
+$22,259/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2286万
+$23,521/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2152万
+$22,461/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2243万
+$23,410/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2057万
+$21,166/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2275万
+$23,404/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2130万
+$22,239/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2133万
+$22,262/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2037万
+$20,956/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2252万
+$23,172/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2109万
+$22,019/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2175万
+$22,704/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2095万
+$21,550/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2142万
+$22,036/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>A | 958呎 (3房)
+$2237万
+$23,347/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>B | 958呎 (3房)
+$2367万
+$24,705/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>C | 972呎 (3房)
+$2157万
+$22,192/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>D | 972呎 (3房)
+$2186万
+$22,493/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$2027万
+$26,226/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$2212万
+$28,620/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1881万
+$25,183/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$2008万
+$27,578/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1951万
+$26,472/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$2100万
+$28,082/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$2012万
+$26,035/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$2068万
+$26,758/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1865万
+$24,971/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1988万
+$27,309/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1849万
+$25,087/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$2080万
+$27,803/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1987万
+$25,709/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$2130万
+$27,558/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1849万
+$24,750/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1978万
+$27,173/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1898万
+$25,760/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1969万
+$26,329/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$2058万
+$26,618/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$2120万
+$27,420/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1830万
+$24,503/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1968万
+$27,037/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1870万
+$25,377/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$2027万
+$27,095/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$2034万
+$26,309/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$2038万
+$26,361/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1745万
+$23,359/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1958万
+$26,902/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1847万
+$25,064/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$2002万
+$26,759/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$2026万
+$26,208/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$2025万
+$26,191/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1736万
+$23,244/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1949万
+$26,769/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1756万
+$23,833/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1973万
+$26,382/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$2023万
+$26,173/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1925万
+$24,907/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1790万
+$23,959/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$2075万
+$28,500/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1811万
+$24,569/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1954万
+$26,122/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1934万
+$25,014/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1995万
+$25,803/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1781万
+$23,839/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1969万
+$27,051/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1802万
+$24,445/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1928万
+$25,771/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$2003万
+$25,913/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$2085万
+$26,974/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1772万
+$23,722/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1906万
+$26,179/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1793万
+$24,324/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1834万
+$24,524/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1914万
+$24,765/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$2075万
+$26,838/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1763万
+$23,605/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1896万
+$26,045/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1713万
+$23,247/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1810万
+$24,191/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1983万
+$25,656/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1887万
+$24,414/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1754万
+$23,486/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1879万
+$25,816/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1705万
+$23,130/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1784万
+$23,854/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1973万
+$25,529/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$2009万
+$25,990/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1746万
+$23,371/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1870万
+$25,687/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1766万
+$23,965/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1849万
+$24,715/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1964万
+$25,401/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1864万
+$24,114/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1972万
+$26,394/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1861万
+$25,559/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1757万
+$23,844/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1839万
+$24,591/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1954万
+$25,276/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1855万
+$23,994/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1728万
+$23,138/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1735万
+$23,831/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1749万
+$23,726/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1830万
+$24,468/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1867万
+$24,157/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1921万
+$24,856/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1720万
+$23,021/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1842万
+$25,305/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1740万
+$23,607/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1821万
+$24,348/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1934万
+$25,025/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1834万
+$23,721/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1711万
+$22,908/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1833万
+$25,181/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1731万
+$23,490/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1812万
+$24,223/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1925万
+$24,900/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1900万
+$24,574/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1636万
+$21,894/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1709万
+$23,478/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1723万
+$23,373/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1803万
+$24,104/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1907万
+$24,670/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1815万
+$23,484/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1694万
+$22,681/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1701万
+$23,361/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1714万
+$23,258/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1794万
+$23,984/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1826万
+$23,617/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1881万
+$24,331/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1686万
+$22,569/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1762万
+$24,202/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1638万
+$22,225/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1785万
+$23,865/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1808万
+$23,383/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1871万
+$24,208/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1678万
+$22,456/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1753万
+$24,081/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1689万
+$22,912/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1767万
+$23,628/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1798万
+$23,266/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1858万
+$24,032/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1920万
+$25,696/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1708万
+$23,466/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1680万
+$22,799/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1759万
+$23,512/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1786万
+$23,111/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1848万
+$23,911/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1661万
+$22,233/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1700万
+$23,348/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1606万
+$21,787/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1750万
+$23,396/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1778万
+$22,995/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1766万
+$22,853/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1653万
+$22,123/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1691万
+$23,231/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1664万
+$22,573/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1959万
+$26,187/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1761万
+$22,781/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1830万
+$23,675/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1581万
+$21,162/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1616万
+$22,203/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1657万
+$22,482/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1949万
+$26,059/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1832万
+$23,705/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1749万
+$22,625/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1638万
+$21,934/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1674万
+$23,000/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1650万
+$22,383/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1724万
+$23,047/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1751万
+$22,656/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1812万
+$23,440/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1630万
+$21,826/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1666万
+$22,887/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1641万
+$22,270/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1716万
+$22,934/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1814万
+$23,470/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1794万
+$23,207/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1620万
+$21,685/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1650万
+$22,661/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1633万
+$22,160/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1707万
+$22,818/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1796万
+$23,238/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1714万
+$22,179/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1608万
+$21,525/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1576万
+$21,655/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1623万
+$22,016/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1690万
+$22,592/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1778万
+$23,008/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1763万
+$22,806/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1600万
+$21,418/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1625万
+$22,324/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1611万
+$21,853/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1673万
+$22,369/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>A | 773呎 (3房)
+$1943万
+$25,140/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>B | 773呎 (3房)
+$1728万
+$22,360/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>C | 747呎 (3房)
+$1706万
+$22,834/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>D | 728呎 (3房)
+$1536万
+$21,099/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1669万
+$22,649/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>F | 748呎 (3房)
+$1777万
+$23,761/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$2011万
+$26,816/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1376万
+$25,578/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1430万
+$26,584/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$1148万
+$25,387/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$1982万
+$25,019/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1121万
+$24,692/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$2028万
+$26,005/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$2051万
+$27,491/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1991万
+$26,552/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1369万
+$25,448/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1367万
+$25,407/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$1142万
+$25,261/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$2011万
+$25,394/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1161万
+$25,577/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$2017万
+$25,862/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1912万
+$25,629/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$2070万
+$27,604/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1418万
+$26,364/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1360万
+$25,281/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$1183万
+$26,170/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$2001万
+$25,266/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1156万
+$25,452/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$2002万
+$25,673/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1968万
+$26,374/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$2032万
+$27,100/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1398万
+$25,981/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1395万
+$25,935/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$1167万
+$25,827/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$1991万
+$25,140/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1150万
+$25,324/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$1986万
+$25,463/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1943万
+$26,046/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1933万
+$25,771/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1387万
+$25,784/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1330万
+$24,725/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$1111万
+$24,582/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$1981万
+$25,015/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1140万
+$25,104/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$1975万
+$25,322/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1843万
+$24,705/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1911万
+$25,479/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1375万
+$25,554/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1318万
+$24,504/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$1142万
+$25,259/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$1971万
+$24,891/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1134万
+$24,978/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$1964万
+$25,179/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1897万
+$25,424/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1970万
+$26,263/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1356万
+$25,197/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1353万
+$25,154/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$1081万
+$23,920/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$2238万
+$28,263/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1128万
+$24,852/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$1944万
+$24,928/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1878万
+$25,173/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1960万
+$26,135/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1285万
+$23,883/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1336万
+$24,823/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$1116万
+$24,679/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$1896万
+$23,937/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1123万
+$24,731/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$1926万
+$24,697/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1787万
+$23,953/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1873万
+$24,975/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1326万
+$24,638/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1323万
+$24,597/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$1066万
+$23,586/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$1870万
+$23,612/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1073万
+$23,634/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$1909万
+$24,469/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1770万
+$23,731/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1864万
+$24,852/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1277万
+$23,729/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1306万
+$24,270/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$1069万
+$23,648/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$1772万
+$22,369/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1112万
+$24,485/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$1890万
+$24,233/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1746万
+$23,408/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1931万
+$25,747/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1269万
+$23,589/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1297万
+$24,110/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$1020万
+$22,577/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$1827万
+$23,072/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1062万
+$23,401/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$1881万
+$24,113/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1793万
+$24,036/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1841万
+$24,545/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1258万
+$23,379/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1282万
+$23,827/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$1012万
+$22,378/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$1810万
+$22,855/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1098万
+$24,189/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$1797万
+$23,044/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1776万
+$23,810/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1832万
+$24,424/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1244万
+$23,126/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1319万
+$24,509/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$1042万
+$23,046/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$1801万
+$22,742/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1030万
+$22,676/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$1788万
+$22,929/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1698万
+$22,755/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1898万
+$25,301/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1233万
+$22,922/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1260万
+$23,422/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$1033万
+$22,845/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$1721万
+$21,734/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1058万
+$23,304/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$1853万
+$23,754/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1759万
+$23,575/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1888万
+$25,177/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1218万
+$22,638/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1306万
+$24,268/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$980万
+$21,670/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$1783万
+$22,516/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1212万
+$26,690/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$1844万
+$23,636/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1750万
+$23,457/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1876万
+$25,016/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1155万
+$21,476/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1299万
+$24,145/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$1007万
+$22,283/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$1774万
+$22,403/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1041万
+$22,923/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$2064万
+$26,459/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1741万
+$23,339/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1867万
+$24,891/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1194万
+$22,193/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1290万
+$23,968/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$1000万
+$22,119/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$1766万
+$22,292/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1034万
+$22,771/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$2112万
+$27,072/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1664万
+$22,306/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1858万
+$24,768/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1141万
+$21,208/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1232万
+$22,905/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$995万
+$22,007/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$1757万
+$22,181/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$1016万
+$22,381/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$1816万
+$23,286/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1724万
+$23,107/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1775万
+$23,668/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1135万
+$21,102/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1277万
+$23,730/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$990万
+$21,898/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$1748万
+$22,071/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$998万
+$21,991/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$1807万
+$23,171/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1715万
+$22,992/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1830万
+$24,399/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1176万
+$21,864/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1218万
+$22,647/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$946万
+$20,929/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 792呎 (3房)
+$1739万
+$21,961/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 454呎 (2房)
+$993万
+$21,879/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 780呎 (3房)
+$1789万
+$22,941/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1698万
+$22,764/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1816万
+$24,220/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1170万
+$21,753/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1572万
+$29,224/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$980万
+$21,681/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 813呎 (3房)
+$1664万
+$20,462/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr"/>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 796呎 (3房)
+$1772万
+$22,256/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1690万
+$22,650/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1808万
+$24,100/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1118万
+$20,788/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1256万
+$23,342/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$975万
+$21,575/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 813呎 (3房)
+$1655万
+$20,360/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr"/>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 796呎 (3房)
+$1693万
+$21,270/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1681万
+$22,539/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1798万
+$23,980/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1159万
+$21,537/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1197万
+$22,255/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$970万
+$21,465/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 813呎 (3房)
+$1715万
+$21,093/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr"/>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 796呎 (3房)
+$1685万
+$21,163/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1673万
+$22,425/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1790万
+$23,861/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1153万
+$21,431/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1240万
+$23,058/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$965万
+$21,358/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 813呎 (3房)
+$1706万
+$20,989/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr"/>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 796呎 (3房)
+$1676万
+$21,060/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1599万
+$21,432/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1781万
+$23,741/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1102万
+$20,481/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1234万
+$22,944/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$923万
+$20,412/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>E | 813呎 (3房)
+$1698万
+$20,884/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr"/>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>G | 796呎 (3房)
+$1668万
+$20,954/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1591万
+$21,326/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1772万
+$23,624/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1143万
+$21,238/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1228万
+$22,829/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$957万
+$21,170/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 813呎 (3房)
+$1785万
+$21,956/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr"/>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 796呎 (3房)
+$1660万
+$20,849/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1813万
+$24,303/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1763万
+$23,505/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1132万
+$21,039/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1528万
+$28,400/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$948万
+$20,969/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>E | 813呎 (3房)
+$1673万
+$20,574/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr"/>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>G | 796呎 (3房)
+$1651万
+$20,746/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1640万
+$21,983/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1676万
+$22,353/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1082万
+$20,108/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1207万
+$22,437/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$943万
+$20,865/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>E | 813呎 (3房)
+$1663万
+$20,454/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr"/>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>G | 796呎 (3房)
+$1635万
+$20,540/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1624万
+$21,764/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1656万
+$22,079/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1113万
+$20,695/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1195万
+$22,214/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$932万
+$20,626/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>E | 813呎 (3房)
+$1642万
+$20,202/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr"/>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>G | 796呎 (3房)
+$1619万
+$20,338/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1608万
+$21,550/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1690万
+$22,539/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>B | 538呎 (2房)
+$1092万
+$20,290/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>C | 538呎 (2房)
+$1125万
+$20,918/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>D | 452呎 (2房)
+$914万
+$20,223/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>E | 813呎 (3房)
+$1544万
+$18,998/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr"/>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
+          <t>G | 796呎 (3房)
+$1652万
+$20,760/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>H | 746呎 (3房)
+$1576万
+$21,126/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
@@ -665,7 +665,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
@@ -5908,7 +5908,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -41583,7 +41583,7 @@
           <t>B | 1267呎 (4+房)
 $3776万
 $29,800/呎
-(26年-06月-21日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Blue Coast.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -128,12 +128,6 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -211,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -274,9 +268,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4655,7 +4646,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -4663,31 +4654,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H65" s="5" t="n">
-        <v>41640000</v>
-      </c>
-      <c r="I65" s="5" t="n">
-        <v>32865</v>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="n">
-        <v>36851400</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>29086</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -25187,30 +25186,38 @@
       </c>
       <c r="F395" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
-        </is>
-      </c>
-      <c r="H395" s="5" t="n">
-        <v>17939000</v>
-      </c>
-      <c r="I395" s="5" t="n">
-        <v>23207</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H395" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I395" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J395" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K395" s="5" t="n">
-        <v>17939000</v>
-      </c>
-      <c r="L395" s="5" t="n">
-        <v>23207</v>
+      <c r="K395" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L395" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M395" s="3" t="inlineStr">
         <is>
@@ -25219,7 +25226,7 @@
       </c>
       <c r="N395" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -34430,14 +34437,14 @@
       </c>
       <c r="G544" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H544" s="5" t="n">
-        <v>21116000</v>
+        <v>20536000</v>
       </c>
       <c r="I544" s="5" t="n">
-        <v>27072</v>
+        <v>26328</v>
       </c>
       <c r="J544" s="3" t="inlineStr">
         <is>
@@ -34445,10 +34452,10 @@
         </is>
       </c>
       <c r="K544" s="5" t="n">
-        <v>21116000</v>
+        <v>20536000</v>
       </c>
       <c r="L544" s="5" t="n">
-        <v>27072</v>
+        <v>26328</v>
       </c>
       <c r="M544" s="3" t="inlineStr">
         <is>
@@ -40733,7 +40740,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -40748,7 +40755,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -41383,12 +41390,12 @@
 (24年-04月-28日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 1267呎 (4+房)
-$4164万
-$32,865/呎
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -43243,17 +43250,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>179</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -44748,12 +44755,12 @@
 (24年-04月-28日)</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 773呎 (3房)
-$1794万
-$23,207/呎
-(24年-05月-06日)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -46294,9 +46301,9 @@
       <c r="H21" s="21" t="inlineStr">
         <is>
           <t>G | 780呎 (3房)
-$2112万
-$27,072/呎
-(26年-05月-20日)</t>
+$2054万
+$26,328/呎
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -46567,7 +46574,7 @@
 (24年-05月-01日)</t>
         </is>
       </c>
-      <c r="G25" s="23" t="inlineStr"/>
+      <c r="G25" s="22" t="inlineStr"/>
       <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
@@ -46631,7 +46638,7 @@
 (24年-05月-01日)</t>
         </is>
       </c>
-      <c r="G26" s="23" t="inlineStr"/>
+      <c r="G26" s="22" t="inlineStr"/>
       <c r="H26" s="21" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
@@ -46695,7 +46702,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="G27" s="23" t="inlineStr"/>
+      <c r="G27" s="22" t="inlineStr"/>
       <c r="H27" s="21" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
@@ -46759,7 +46766,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="G28" s="23" t="inlineStr"/>
+      <c r="G28" s="22" t="inlineStr"/>
       <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
@@ -46823,7 +46830,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="G29" s="23" t="inlineStr"/>
+      <c r="G29" s="22" t="inlineStr"/>
       <c r="H29" s="21" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
@@ -46887,7 +46894,7 @@
 (24年-08月-04日)</t>
         </is>
       </c>
-      <c r="G30" s="23" t="inlineStr"/>
+      <c r="G30" s="22" t="inlineStr"/>
       <c r="H30" s="21" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
@@ -46951,7 +46958,7 @@
 (24年-05月-02日)</t>
         </is>
       </c>
-      <c r="G31" s="23" t="inlineStr"/>
+      <c r="G31" s="22" t="inlineStr"/>
       <c r="H31" s="21" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
@@ -47015,7 +47022,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="G32" s="23" t="inlineStr"/>
+      <c r="G32" s="22" t="inlineStr"/>
       <c r="H32" s="21" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
@@ -47079,7 +47086,7 @@
 (24年-04月-24日)</t>
         </is>
       </c>
-      <c r="G33" s="23" t="inlineStr"/>
+      <c r="G33" s="22" t="inlineStr"/>
       <c r="H33" s="21" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
@@ -47143,7 +47150,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="G34" s="23" t="inlineStr"/>
+      <c r="G34" s="22" t="inlineStr"/>
       <c r="H34" s="21" t="inlineStr">
         <is>
           <t>G | 796呎 (3房)
